--- a/hk/数据通路表、控制信号取值表_miniRV-完整.xlsx
+++ b/hk/数据通路表、控制信号取值表_miniRV-完整.xlsx
@@ -6409,12 +6409,12 @@
       </c>
       <c r="K5" s="76" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="L5" s="76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_EXT_N</t>
         </is>
       </c>
       <c r="M5" s="26" t="n"/>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="K6" s="76" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="L6" s="76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_EXT_N</t>
         </is>
       </c>
       <c r="M6" s="26" t="n"/>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="K7" s="76" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="L7" s="76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_EXT_N</t>
         </is>
       </c>
       <c r="M7" s="26" t="n"/>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="L8" s="76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_EXT_N</t>
         </is>
       </c>
       <c r="M8" s="26" t="n"/>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="K9" s="76" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="L9" s="76" t="inlineStr">
         <is>
-          <t>WORD_EXT</t>
+          <t>RAM_EXT_W</t>
         </is>
       </c>
       <c r="M9" s="26" t="n"/>
@@ -6707,12 +6707,12 @@
       </c>
       <c r="K10" s="76" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="L10" s="76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_EXT_N</t>
         </is>
       </c>
       <c r="M10" s="26" t="n"/>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="K11" s="76" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="L11" s="76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_EXT_N</t>
         </is>
       </c>
       <c r="M11" s="26" t="n"/>
@@ -6828,13 +6828,15 @@
       </c>
       <c r="L12" s="76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_EXT_N</t>
         </is>
       </c>
       <c r="M12" s="26" t="n"/>
       <c r="N12" s="26" t="n"/>
       <c r="O12" s="26" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="100" t="inlineStr">
         <is>
@@ -6981,17 +6983,17 @@
       </c>
       <c r="K17" s="82" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L17" s="82" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M17" s="80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N17" s="80" t="inlineStr">
@@ -7058,17 +7060,17 @@
       </c>
       <c r="K18" s="82" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L18" s="82" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M18" s="80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N18" s="80" t="inlineStr">
@@ -7135,17 +7137,17 @@
       </c>
       <c r="K19" s="82" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L19" s="82" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M19" s="80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N19" s="80" t="inlineStr">
@@ -7212,17 +7214,17 @@
       </c>
       <c r="K20" s="82" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L20" s="82" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M20" s="80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N20" s="80" t="inlineStr">
@@ -7289,17 +7291,17 @@
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L21" s="82" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M21" s="80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N21" s="80" t="inlineStr">
@@ -7366,17 +7368,17 @@
       </c>
       <c r="K22" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L22" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M22" s="80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N22" s="80" t="inlineStr">
@@ -7443,17 +7445,17 @@
       </c>
       <c r="K23" s="80" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L23" s="80" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M23" s="80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N23" s="80" t="inlineStr">
@@ -7520,17 +7522,17 @@
       </c>
       <c r="K24" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L24" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M24" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N24" s="69" t="inlineStr">
@@ -7597,17 +7599,17 @@
       </c>
       <c r="K25" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L25" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M25" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N25" s="69" t="inlineStr">
@@ -7674,17 +7676,17 @@
       </c>
       <c r="K26" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L26" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M26" s="69" t="inlineStr">
         <is>
-          <t>WORD_EXT</t>
+          <t>RAM_EXT_W</t>
         </is>
       </c>
       <c r="N26" s="69" t="inlineStr">
@@ -7751,17 +7753,17 @@
       </c>
       <c r="K27" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L27" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M27" s="69" t="inlineStr">
         <is>
-          <t>BYTE_EXT</t>
+          <t>RAM_EXT_B</t>
         </is>
       </c>
       <c r="N27" s="69" t="inlineStr">
@@ -7828,17 +7830,17 @@
       </c>
       <c r="K28" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L28" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M28" s="69" t="inlineStr">
         <is>
-          <t>BYTEU_EXT</t>
+          <t>RAM_EXT_BU</t>
         </is>
       </c>
       <c r="N28" s="69" t="inlineStr">
@@ -7905,17 +7907,17 @@
       </c>
       <c r="K29" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L29" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M29" s="69" t="inlineStr">
         <is>
-          <t>HALF_EXT</t>
+          <t>RAM_EXT_H</t>
         </is>
       </c>
       <c r="N29" s="69" t="inlineStr">
@@ -7982,17 +7984,17 @@
       </c>
       <c r="K30" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L30" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M30" s="69" t="inlineStr">
         <is>
-          <t>HALFU_EXT</t>
+          <t>RAM_EXT_HU</t>
         </is>
       </c>
       <c r="N30" s="69" t="inlineStr">
@@ -8059,17 +8061,17 @@
       </c>
       <c r="K31" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L31" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M31" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N31" s="69" t="inlineStr">
@@ -8136,17 +8138,17 @@
       </c>
       <c r="K32" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L32" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M32" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N32" s="69" t="inlineStr">
@@ -8213,17 +8215,17 @@
       </c>
       <c r="K33" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L33" s="69" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M33" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N33" s="69" t="inlineStr">
@@ -8290,17 +8292,17 @@
       </c>
       <c r="K34" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L34" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M34" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N34" s="69" t="inlineStr">
@@ -8367,17 +8369,17 @@
       </c>
       <c r="K35" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L35" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M35" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N35" s="69" t="inlineStr">
@@ -8444,17 +8446,17 @@
       </c>
       <c r="K36" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L36" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M36" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N36" s="69" t="inlineStr">
@@ -8521,17 +8523,17 @@
       </c>
       <c r="K37" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L37" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M37" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N37" s="69" t="inlineStr">
@@ -8598,17 +8600,17 @@
       </c>
       <c r="K38" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L38" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M38" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N38" s="69" t="inlineStr">
@@ -8675,17 +8677,17 @@
       </c>
       <c r="K39" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L39" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M39" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N39" s="69" t="inlineStr">
@@ -8752,17 +8754,17 @@
       </c>
       <c r="K40" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L40" s="69" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M40" s="69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N40" s="69" t="inlineStr">
@@ -8829,17 +8831,17 @@
       </c>
       <c r="K41" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L41" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M41" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N41" s="70" t="inlineStr">
@@ -8906,17 +8908,17 @@
       </c>
       <c r="K42" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L42" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M42" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N42" s="70" t="inlineStr">
@@ -8983,17 +8985,17 @@
       </c>
       <c r="K43" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L43" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M43" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N43" s="70" t="inlineStr">
@@ -9060,17 +9062,17 @@
       </c>
       <c r="K44" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L44" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M44" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N44" s="70" t="inlineStr">
@@ -9137,17 +9139,17 @@
       </c>
       <c r="K45" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L45" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M45" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N45" s="70" t="inlineStr">
@@ -9214,17 +9216,17 @@
       </c>
       <c r="K46" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L46" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M46" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N46" s="70" t="inlineStr">
@@ -9291,17 +9293,17 @@
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L47" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M47" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N47" s="70" t="inlineStr">
@@ -9368,17 +9370,17 @@
       </c>
       <c r="K48" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L48" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M48" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N48" s="70" t="inlineStr">
@@ -9445,17 +9447,17 @@
       </c>
       <c r="K49" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L49" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M49" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N49" s="70" t="inlineStr">
@@ -9522,17 +9524,17 @@
       </c>
       <c r="K50" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L50" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M50" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N50" s="70" t="inlineStr">
@@ -9599,17 +9601,17 @@
       </c>
       <c r="K51" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L51" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M51" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N51" s="70" t="inlineStr">
@@ -9676,17 +9678,17 @@
       </c>
       <c r="K52" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L52" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M52" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N52" s="70" t="inlineStr">
@@ -9753,17 +9755,17 @@
       </c>
       <c r="K53" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L53" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M53" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N53" s="70" t="inlineStr">
@@ -9830,17 +9832,17 @@
       </c>
       <c r="K54" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L54" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M54" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N54" s="70" t="inlineStr">
@@ -9907,17 +9909,17 @@
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L55" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M55" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N55" s="70" t="inlineStr">
@@ -9984,17 +9986,17 @@
       </c>
       <c r="K56" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L56" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS2</t>
+          <t>ALU_B_RS2</t>
         </is>
       </c>
       <c r="M56" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N56" s="70" t="inlineStr">
@@ -10071,7 +10073,7 @@
       </c>
       <c r="M57" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N57" s="70" t="inlineStr">
@@ -10138,17 +10140,17 @@
       </c>
       <c r="K58" s="70" t="inlineStr">
         <is>
-          <t>SEL_PC</t>
+          <t>ALU_A_PC</t>
         </is>
       </c>
       <c r="L58" s="70" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M58" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N58" s="70" t="inlineStr">
@@ -10225,7 +10227,7 @@
       </c>
       <c r="M59" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N59" s="70" t="inlineStr">
@@ -10292,17 +10294,17 @@
       </c>
       <c r="K60" s="70" t="inlineStr">
         <is>
-          <t>SEL_RS1</t>
+          <t>ALU_A_RS1</t>
         </is>
       </c>
       <c r="L60" s="70" t="inlineStr">
         <is>
-          <t>SEL_EXT</t>
+          <t>ALU_B_EXT</t>
         </is>
       </c>
       <c r="M60" s="70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RAM_WE_N</t>
         </is>
       </c>
       <c r="N60" s="70" t="inlineStr">

--- a/hk/数据通路表、控制信号取值表_miniRV-完整.xlsx
+++ b/hk/数据通路表、控制信号取值表_miniRV-完整.xlsx
@@ -2113,6 +2113,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="68" t="inlineStr">
         <is>
@@ -6242,7 +6244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:P60"/>
+  <dimension ref="A2:P60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.07421875" defaultRowHeight="15.5"/>
   <cols>
     <col width="3.69140625" customWidth="1" style="55" min="1" max="1"/>
